--- a/data/products_master_v25.xlsx
+++ b/data/products_master_v25.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491BAB3B-D9B7-4833-8111-5B8CC79D1AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6268E4B8-5FDC-42AC-9B7F-C2F7E190620C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1410" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="978">
   <si>
     <t>product_number</t>
   </si>
@@ -2531,10 +2531,6 @@
   </si>
   <si>
     <t>A VIP Premium Dental Clinic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>#P-001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -6315,6 +6311,14 @@
   </si>
   <si>
     <t>INSPIRE - Sun Tower Inspire Suite(Premier Suite Journey)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                   </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                         </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -7012,7 +7016,7 @@
     </row>
     <row r="2" spans="1:30" s="2" customFormat="1" ht="365.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>728</v>
+        <v>976</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -7054,7 +7058,7 @@
         <v>32</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>31</v>
@@ -7143,7 +7147,7 @@
         <v>32</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>31</v>
@@ -7232,7 +7236,7 @@
         <v>32</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>31</v>
@@ -7321,7 +7325,7 @@
         <v>32</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
@@ -7401,7 +7405,7 @@
         <v>32</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
@@ -7481,7 +7485,7 @@
         <v>32</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
@@ -7552,7 +7556,7 @@
         <v>32</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -7623,7 +7627,7 @@
         <v>32</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
@@ -7703,7 +7707,7 @@
         <v>32</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
@@ -7783,7 +7787,7 @@
         <v>32</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
@@ -8010,7 +8014,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>546</v>
@@ -8090,7 +8094,7 @@
         <v>27</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>546</v>
@@ -8170,7 +8174,7 @@
         <v>27</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>546</v>
@@ -8250,7 +8254,7 @@
         <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>546</v>
@@ -8333,7 +8337,7 @@
         <v>27</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>546</v>
@@ -8416,7 +8420,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>552</v>
@@ -8499,7 +8503,7 @@
         <v>27</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>555</v>
@@ -8579,7 +8583,7 @@
         <v>27</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>556</v>
@@ -8662,7 +8666,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>556</v>
@@ -8745,7 +8749,7 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>556</v>
@@ -8828,7 +8832,7 @@
         <v>27</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>552</v>
@@ -8911,7 +8915,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>556</v>
@@ -8994,7 +8998,7 @@
         <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>559</v>
@@ -9077,7 +9081,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>559</v>
@@ -9160,7 +9164,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>546</v>
@@ -9240,7 +9244,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>546</v>
@@ -9317,7 +9321,7 @@
         <v>27</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>546</v>
@@ -9394,7 +9398,7 @@
         <v>27</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>552</v>
@@ -9406,7 +9410,7 @@
         <v>657</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K32" s="2">
         <v>10000000</v>
@@ -9421,7 +9425,7 @@
         <v>659</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
@@ -9441,7 +9445,7 @@
         <v>27</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>552</v>
@@ -9453,7 +9457,7 @@
         <v>657</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K33" s="2">
         <v>30000000</v>
@@ -9468,7 +9472,7 @@
         <v>659</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
@@ -9488,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>552</v>
@@ -9500,7 +9504,7 @@
         <v>657</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K34" s="2">
         <v>70000000</v>
@@ -9515,7 +9519,7 @@
         <v>659</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
@@ -9568,7 +9572,7 @@
         <v>52</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>588</v>
@@ -9627,7 +9631,7 @@
         <v>52</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
@@ -9784,7 +9788,7 @@
         <v>709</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>635</v>
@@ -9820,7 +9824,7 @@
         <v>52</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>223</v>
@@ -9870,7 +9874,7 @@
         <v>710</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>635</v>
@@ -9906,7 +9910,7 @@
         <v>52</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>223</v>
@@ -9956,7 +9960,7 @@
         <v>711</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>636</v>
@@ -9992,7 +9996,7 @@
         <v>52</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>226</v>
@@ -10042,7 +10046,7 @@
         <v>712</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>636</v>
@@ -10078,7 +10082,7 @@
         <v>52</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>230</v>
@@ -10128,7 +10132,7 @@
         <v>713</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>636</v>
@@ -10164,7 +10168,7 @@
         <v>31</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>233</v>
@@ -10214,7 +10218,7 @@
         <v>714</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>636</v>
@@ -10250,7 +10254,7 @@
         <v>31</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>237</v>
@@ -10298,7 +10302,7 @@
         <v>715</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>636</v>
@@ -10334,7 +10338,7 @@
         <v>52</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>241</v>
@@ -10384,7 +10388,7 @@
         <v>716</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>636</v>
@@ -10420,7 +10424,7 @@
         <v>52</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>244</v>
@@ -10646,7 +10650,7 @@
         <v>52</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="3" t="s">
@@ -10721,7 +10725,7 @@
         <v>52</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
@@ -10794,7 +10798,7 @@
         <v>52</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
@@ -10920,7 +10924,7 @@
         <v>52</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
@@ -10973,7 +10977,7 @@
         <v>52</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>166</v>
@@ -11051,7 +11055,7 @@
         <v>52</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>166</v>
@@ -11137,7 +11141,7 @@
         <v>31</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>180</v>
@@ -11224,7 +11228,7 @@
         <v>31</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>187</v>
@@ -11311,7 +11315,7 @@
         <v>31</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>192</v>
@@ -11398,7 +11402,7 @@
         <v>32</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>200</v>
@@ -11487,7 +11491,7 @@
         <v>32</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>204</v>
@@ -11574,7 +11578,7 @@
         <v>32</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>207</v>
@@ -11661,7 +11665,7 @@
         <v>32</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>211</v>
@@ -11680,7 +11684,7 @@
         <v>31</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>31</v>
@@ -11748,7 +11752,7 @@
         <v>32</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>214</v>
@@ -11767,7 +11771,7 @@
         <v>79</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>31</v>
@@ -11835,7 +11839,7 @@
         <v>52</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>217</v>
@@ -11854,7 +11858,7 @@
         <v>31</v>
       </c>
       <c r="V17" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="W17" s="2" t="s">
         <v>31</v>
@@ -11922,7 +11926,7 @@
         <v>32</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>248</v>
@@ -11941,7 +11945,7 @@
         <v>79</v>
       </c>
       <c r="V18" s="6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>31</v>
@@ -12009,7 +12013,7 @@
         <v>106</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>253</v>
@@ -12028,7 +12032,7 @@
         <v>134</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="Z19" s="2" t="b">
         <v>1</v>
@@ -12090,7 +12094,7 @@
         <v>106</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>259</v>
@@ -12109,7 +12113,7 @@
         <v>136</v>
       </c>
       <c r="V20" s="6" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="Z20" s="2" t="b">
         <v>1</v>
@@ -12171,7 +12175,7 @@
         <v>32</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>261</v>
@@ -12190,7 +12194,7 @@
         <v>79</v>
       </c>
       <c r="V21" s="6" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="Z21" s="2" t="b">
         <v>1</v>
@@ -12252,7 +12256,7 @@
         <v>106</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>265</v>
@@ -12271,7 +12275,7 @@
         <v>136</v>
       </c>
       <c r="V22" s="6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="Z22" s="2" t="b">
         <v>1</v>
@@ -12333,7 +12337,7 @@
         <v>32</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>269</v>
@@ -12352,7 +12356,7 @@
         <v>31</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>31</v>
@@ -12420,7 +12424,7 @@
         <v>32</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>273</v>
@@ -12439,7 +12443,7 @@
         <v>31</v>
       </c>
       <c r="V24" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="W24" s="2" t="s">
         <v>31</v>
@@ -12507,7 +12511,7 @@
         <v>32</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>278</v>
@@ -12526,7 +12530,7 @@
         <v>31</v>
       </c>
       <c r="V25" s="6" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="W25" s="2" t="s">
         <v>31</v>
@@ -12594,7 +12598,7 @@
         <v>32</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>283</v>
@@ -12613,7 +12617,7 @@
         <v>140</v>
       </c>
       <c r="V26" s="6" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="W26" s="2" t="s">
         <v>31</v>
@@ -12681,7 +12685,7 @@
         <v>32</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>288</v>
@@ -12700,7 +12704,7 @@
         <v>142</v>
       </c>
       <c r="V27" s="6" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="W27" s="2" t="s">
         <v>31</v>
@@ -12744,7 +12748,7 @@
         <v>293</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>294</v>
@@ -12768,7 +12772,7 @@
         <v>32</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>297</v>
@@ -12787,7 +12791,7 @@
         <v>144</v>
       </c>
       <c r="V28" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="W28" s="2" t="s">
         <v>31</v>
@@ -12831,7 +12835,7 @@
         <v>293</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>294</v>
@@ -12855,7 +12859,7 @@
         <v>32</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>297</v>
@@ -12874,7 +12878,7 @@
         <v>144</v>
       </c>
       <c r="V29" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="W29" s="2" t="s">
         <v>31</v>
@@ -12918,7 +12922,7 @@
         <v>303</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>304</v>
@@ -12942,7 +12946,7 @@
         <v>32</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>305</v>
@@ -12961,7 +12965,7 @@
         <v>31</v>
       </c>
       <c r="V30" s="6" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="W30" s="2" t="s">
         <v>31</v>
@@ -13005,7 +13009,7 @@
         <v>303</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>304</v>
@@ -13029,7 +13033,7 @@
         <v>32</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>305</v>
@@ -13092,7 +13096,7 @@
         <v>311</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>312</v>
@@ -13116,7 +13120,7 @@
         <v>32</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>313</v>
@@ -13135,7 +13139,7 @@
         <v>146</v>
       </c>
       <c r="V32" s="6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="W32" s="2" t="s">
         <v>31</v>
@@ -13179,7 +13183,7 @@
         <v>311</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>312</v>
@@ -13203,7 +13207,7 @@
         <v>32</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>313</v>
@@ -13266,7 +13270,7 @@
         <v>317</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>318</v>
@@ -13290,7 +13294,7 @@
         <v>32</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>319</v>
@@ -13309,7 +13313,7 @@
         <v>149</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>31</v>
@@ -13353,7 +13357,7 @@
         <v>317</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>318</v>
@@ -13377,7 +13381,7 @@
         <v>32</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>319</v>
@@ -13446,7 +13450,7 @@
         <v>323</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>31</v>
@@ -13464,7 +13468,7 @@
         <v>32</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>324</v>
@@ -13483,7 +13487,7 @@
         <v>31</v>
       </c>
       <c r="V36" s="6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>31</v>
@@ -13533,7 +13537,7 @@
         <v>323</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>31</v>
@@ -13551,7 +13555,7 @@
         <v>32</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>324</v>
@@ -13636,7 +13640,7 @@
         <v>32</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>324</v>
@@ -13721,7 +13725,7 @@
         <v>32</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>324</v>
@@ -13790,7 +13794,7 @@
         <v>330</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>31</v>
@@ -13808,7 +13812,7 @@
         <v>32</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>331</v>
@@ -13827,7 +13831,7 @@
         <v>152</v>
       </c>
       <c r="V40" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>31</v>
@@ -13877,7 +13881,7 @@
         <v>330</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>31</v>
@@ -13895,7 +13899,7 @@
         <v>32</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>331</v>
@@ -13980,7 +13984,7 @@
         <v>32</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>331</v>
@@ -14065,7 +14069,7 @@
         <v>32</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>331</v>
@@ -14152,7 +14156,7 @@
         <v>106</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>336</v>
@@ -14171,7 +14175,7 @@
         <v>92</v>
       </c>
       <c r="V44" s="6" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="W44" s="2" t="s">
         <v>31</v>
@@ -14239,7 +14243,7 @@
         <v>106</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>336</v>
@@ -14326,7 +14330,7 @@
         <v>32</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>343</v>
@@ -14345,7 +14349,7 @@
         <v>31</v>
       </c>
       <c r="V46" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>31</v>
@@ -14413,7 +14417,7 @@
         <v>32</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>347</v>
@@ -14432,7 +14436,7 @@
         <v>31</v>
       </c>
       <c r="V47" s="6" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="W47" s="2" t="s">
         <v>31</v>
@@ -14500,7 +14504,7 @@
         <v>106</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>352</v>
@@ -14587,7 +14591,7 @@
         <v>106</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>352</v>
@@ -14674,7 +14678,7 @@
         <v>106</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="P50" s="3" t="s">
         <v>360</v>
@@ -14761,7 +14765,7 @@
         <v>106</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>360</v>
@@ -14848,7 +14852,7 @@
         <v>106</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>366</v>
@@ -14935,7 +14939,7 @@
         <v>32</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P53" s="3" t="s">
         <v>373</v>
@@ -15022,7 +15026,7 @@
         <v>32</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>373</v>
@@ -15109,7 +15113,7 @@
         <v>32</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P55" s="3" t="s">
         <v>378</v>
@@ -15196,7 +15200,7 @@
         <v>32</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="P56" s="3" t="s">
         <v>382</v>
@@ -15452,7 +15456,7 @@
         <v>32</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>388</v>
@@ -15535,7 +15539,7 @@
         <v>32</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>388</v>
@@ -15618,7 +15622,7 @@
         <v>32</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>388</v>
@@ -15746,7 +15750,7 @@
         <v>13</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>15</v>
@@ -15838,7 +15842,7 @@
         <v>32</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>57</v>
@@ -15856,7 +15860,7 @@
         <v>79</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>31</v>
@@ -15924,7 +15928,7 @@
         <v>32</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>57</v>
@@ -15942,7 +15946,7 @@
         <v>79</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>31</v>
@@ -16010,7 +16014,7 @@
         <v>32</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>57</v>
@@ -16028,7 +16032,7 @@
         <v>79</v>
       </c>
       <c r="X4" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>31</v>
@@ -16110,7 +16114,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -16181,7 +16185,7 @@
     </row>
     <row r="2" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>400</v>
@@ -16190,7 +16194,7 @@
         <v>407</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>408</v>
@@ -16199,7 +16203,7 @@
         <v>409</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>31</v>
@@ -16220,7 +16224,7 @@
         <v>32</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
@@ -16247,7 +16251,7 @@
     </row>
     <row r="3" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>400</v>
@@ -16256,7 +16260,7 @@
         <v>407</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>408</v>
@@ -16265,7 +16269,7 @@
         <v>409</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>31</v>
@@ -16286,7 +16290,7 @@
         <v>32</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3" t="s">
@@ -16313,7 +16317,7 @@
     </row>
     <row r="4" spans="1:28" s="2" customFormat="1" ht="132" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>400</v>
@@ -16322,7 +16326,7 @@
         <v>407</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>408</v>
@@ -16331,7 +16335,7 @@
         <v>409</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>31</v>
@@ -16352,7 +16356,7 @@
         <v>32</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
@@ -16379,7 +16383,7 @@
     </row>
     <row r="5" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>400</v>
@@ -16388,7 +16392,7 @@
         <v>407</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>408</v>
@@ -16397,7 +16401,7 @@
         <v>409</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>31</v>
@@ -16418,7 +16422,7 @@
         <v>32</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3" t="s">
@@ -16445,7 +16449,7 @@
     </row>
     <row r="6" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>400</v>
@@ -16454,7 +16458,7 @@
         <v>407</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>412</v>
@@ -16463,7 +16467,7 @@
         <v>413</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>31</v>
@@ -16484,7 +16488,7 @@
         <v>32</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3" t="s">
@@ -16511,7 +16515,7 @@
     </row>
     <row r="7" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>400</v>
@@ -16520,7 +16524,7 @@
         <v>407</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>412</v>
@@ -16529,7 +16533,7 @@
         <v>413</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>31</v>
@@ -16550,7 +16554,7 @@
         <v>32</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3" t="s">
@@ -16577,7 +16581,7 @@
     </row>
     <row r="8" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>400</v>
@@ -16586,7 +16590,7 @@
         <v>407</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>412</v>
@@ -16595,7 +16599,7 @@
         <v>413</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>31</v>
@@ -16616,7 +16620,7 @@
         <v>32</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
@@ -16643,7 +16647,7 @@
     </row>
     <row r="9" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>400</v>
@@ -16652,7 +16656,7 @@
         <v>407</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>412</v>
@@ -16661,7 +16665,7 @@
         <v>413</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>31</v>
@@ -16682,7 +16686,7 @@
         <v>32</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
@@ -16709,7 +16713,7 @@
     </row>
     <row r="10" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>400</v>
@@ -16718,7 +16722,7 @@
         <v>407</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>415</v>
@@ -16727,7 +16731,7 @@
         <v>416</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>31</v>
@@ -16748,7 +16752,7 @@
         <v>32</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
@@ -16775,7 +16779,7 @@
     </row>
     <row r="11" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>400</v>
@@ -16784,7 +16788,7 @@
         <v>407</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>415</v>
@@ -16793,7 +16797,7 @@
         <v>416</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>31</v>
@@ -16814,7 +16818,7 @@
         <v>32</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3" t="s">
@@ -16841,7 +16845,7 @@
     </row>
     <row r="12" spans="1:28" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>400</v>
@@ -16850,7 +16854,7 @@
         <v>407</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>418</v>
@@ -16859,7 +16863,7 @@
         <v>419</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>31</v>
@@ -16880,7 +16884,7 @@
         <v>32</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3" t="s">
@@ -16907,7 +16911,7 @@
     </row>
     <row r="13" spans="1:28" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>400</v>
@@ -16916,7 +16920,7 @@
         <v>407</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>418</v>
@@ -16925,7 +16929,7 @@
         <v>419</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>31</v>
@@ -16946,7 +16950,7 @@
         <v>32</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3" t="s">
@@ -16973,7 +16977,7 @@
     </row>
     <row r="14" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>400</v>
@@ -16982,7 +16986,7 @@
         <v>407</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>420</v>
@@ -16991,7 +16995,7 @@
         <v>420</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>31</v>
@@ -17012,7 +17016,7 @@
         <v>32</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3" t="s">
@@ -17039,7 +17043,7 @@
     </row>
     <row r="15" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>400</v>
@@ -17048,7 +17052,7 @@
         <v>407</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>420</v>
@@ -17057,7 +17061,7 @@
         <v>420</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>31</v>
@@ -17078,7 +17082,7 @@
         <v>32</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3" t="s">
@@ -17105,7 +17109,7 @@
     </row>
     <row r="16" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>400</v>
@@ -17114,7 +17118,7 @@
         <v>407</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>420</v>
@@ -17123,7 +17127,7 @@
         <v>420</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>31</v>
@@ -17144,7 +17148,7 @@
         <v>32</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
@@ -17171,7 +17175,7 @@
     </row>
     <row r="17" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>400</v>
@@ -17180,7 +17184,7 @@
         <v>407</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>421</v>
@@ -17189,7 +17193,7 @@
         <v>422</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>31</v>
@@ -17210,7 +17214,7 @@
         <v>32</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3" t="s">
@@ -17237,7 +17241,7 @@
     </row>
     <row r="18" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>400</v>
@@ -17246,7 +17250,7 @@
         <v>407</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>421</v>
@@ -17255,7 +17259,7 @@
         <v>422</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>31</v>
@@ -17276,7 +17280,7 @@
         <v>32</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3" t="s">
@@ -17303,7 +17307,7 @@
     </row>
     <row r="19" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>400</v>
@@ -17312,7 +17316,7 @@
         <v>407</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>421</v>
@@ -17321,7 +17325,7 @@
         <v>422</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>31</v>
@@ -17342,7 +17346,7 @@
         <v>32</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3" t="s">
@@ -17369,7 +17373,7 @@
     </row>
     <row r="20" spans="1:28" s="2" customFormat="1" ht="132" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>400</v>
@@ -17378,7 +17382,7 @@
         <v>407</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>424</v>
@@ -17387,7 +17391,7 @@
         <v>424</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>31</v>
@@ -17409,7 +17413,7 @@
         <v>32</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3" t="s">
@@ -17436,7 +17440,7 @@
     </row>
     <row r="21" spans="1:28" s="2" customFormat="1" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>400</v>
@@ -17445,7 +17449,7 @@
         <v>407</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>424</v>
@@ -17454,7 +17458,7 @@
         <v>424</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>31</v>
@@ -17476,7 +17480,7 @@
         <v>32</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3" t="s">
@@ -17503,7 +17507,7 @@
     </row>
     <row r="22" spans="1:28" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>400</v>
@@ -17512,7 +17516,7 @@
         <v>407</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>425</v>
@@ -17521,7 +17525,7 @@
         <v>426</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>31</v>
@@ -17542,7 +17546,7 @@
         <v>32</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3" t="s">
@@ -17569,7 +17573,7 @@
     </row>
     <row r="23" spans="1:28" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>400</v>
@@ -17578,7 +17582,7 @@
         <v>407</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>425</v>
@@ -17587,7 +17591,7 @@
         <v>426</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>31</v>
@@ -17608,7 +17612,7 @@
         <v>32</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3" t="s">
@@ -17635,7 +17639,7 @@
     </row>
     <row r="24" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>400</v>
@@ -17644,7 +17648,7 @@
         <v>407</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>427</v>
@@ -17653,7 +17657,7 @@
         <v>428</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>31</v>
@@ -17674,7 +17678,7 @@
         <v>32</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3" t="s">
@@ -17701,7 +17705,7 @@
     </row>
     <row r="25" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>400</v>
@@ -17710,7 +17714,7 @@
         <v>407</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>427</v>
@@ -17719,7 +17723,7 @@
         <v>428</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>31</v>
@@ -17740,7 +17744,7 @@
         <v>32</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3" t="s">
@@ -17767,7 +17771,7 @@
     </row>
     <row r="26" spans="1:28" s="2" customFormat="1" ht="132" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>400</v>
@@ -17776,7 +17780,7 @@
         <v>407</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>430</v>
@@ -17785,7 +17789,7 @@
         <v>430</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>31</v>
@@ -17806,7 +17810,7 @@
         <v>32</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3" t="s">
@@ -17833,7 +17837,7 @@
     </row>
     <row r="27" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>400</v>
@@ -17842,7 +17846,7 @@
         <v>407</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>432</v>
@@ -17851,7 +17855,7 @@
         <v>433</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>31</v>
@@ -17872,7 +17876,7 @@
         <v>32</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3" t="s">
@@ -17899,7 +17903,7 @@
     </row>
     <row r="28" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>400</v>
@@ -17908,7 +17912,7 @@
         <v>407</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>435</v>
@@ -17917,7 +17921,7 @@
         <v>435</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>31</v>
@@ -17938,7 +17942,7 @@
         <v>32</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3" t="s">
@@ -17965,7 +17969,7 @@
     </row>
     <row r="29" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>400</v>
@@ -17974,7 +17978,7 @@
         <v>407</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>847</v>
+        <v>977</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>436</v>
@@ -17983,7 +17987,7 @@
         <v>437</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>31</v>
@@ -18004,7 +18008,7 @@
         <v>32</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3" t="s">
@@ -18031,7 +18035,7 @@
     </row>
     <row r="30" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>400</v>
@@ -18040,7 +18044,7 @@
         <v>407</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>436</v>
@@ -18049,7 +18053,7 @@
         <v>437</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>31</v>
@@ -18070,7 +18074,7 @@
         <v>32</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3" t="s">
@@ -18097,7 +18101,7 @@
     </row>
     <row r="31" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>400</v>
@@ -18106,7 +18110,7 @@
         <v>407</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>436</v>
@@ -18115,7 +18119,7 @@
         <v>437</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>31</v>
@@ -18136,7 +18140,7 @@
         <v>32</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3" t="s">
@@ -18163,7 +18167,7 @@
     </row>
     <row r="32" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>400</v>
@@ -18172,7 +18176,7 @@
         <v>407</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>436</v>
@@ -18181,7 +18185,7 @@
         <v>437</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>31</v>
@@ -18202,7 +18206,7 @@
         <v>32</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3" t="s">
@@ -18229,7 +18233,7 @@
     </row>
     <row r="33" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>400</v>
@@ -18238,7 +18242,7 @@
         <v>407</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>436</v>
@@ -18247,7 +18251,7 @@
         <v>437</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>31</v>
@@ -18268,7 +18272,7 @@
         <v>32</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
@@ -18295,7 +18299,7 @@
     </row>
     <row r="34" spans="1:28" s="2" customFormat="1" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>400</v>
@@ -18321,6 +18325,9 @@
       <c r="L34" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="M34" s="17">
+        <v>100000</v>
+      </c>
       <c r="N34" s="2">
         <v>8</v>
       </c>
@@ -18328,7 +18335,7 @@
         <v>649</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3" t="s">
@@ -18355,7 +18362,7 @@
     </row>
     <row r="35" spans="1:28" s="2" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>400</v>
@@ -18384,6 +18391,9 @@
       <c r="L35" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="M35" s="17">
+        <v>100000</v>
+      </c>
       <c r="N35" s="2">
         <v>10</v>
       </c>
@@ -18391,7 +18401,7 @@
         <v>649</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3" t="s">
@@ -18418,7 +18428,7 @@
     </row>
     <row r="36" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>400</v>
@@ -18460,7 +18470,7 @@
         <v>106</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3" t="s">
@@ -18487,7 +18497,7 @@
     </row>
     <row r="37" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>400</v>
@@ -18529,7 +18539,7 @@
         <v>106</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3" t="s">
@@ -18556,7 +18566,7 @@
     </row>
     <row r="38" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>400</v>
@@ -18598,7 +18608,7 @@
         <v>106</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3" t="s">
@@ -18625,7 +18635,7 @@
     </row>
     <row r="39" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>400</v>
@@ -18667,7 +18677,7 @@
         <v>106</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
@@ -18694,7 +18704,7 @@
     </row>
     <row r="40" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>400</v>
@@ -18709,7 +18719,7 @@
         <v>449</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>450</v>
@@ -18736,7 +18746,7 @@
         <v>31</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="Q40" s="3"/>
       <c r="R40" s="3" t="s">
@@ -18763,7 +18773,7 @@
     </row>
     <row r="41" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>400</v>
@@ -18778,7 +18788,7 @@
         <v>455</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>31</v>
@@ -18799,7 +18809,7 @@
         <v>106</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
@@ -18826,7 +18836,7 @@
     </row>
     <row r="42" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>400</v>
@@ -18841,7 +18851,7 @@
         <v>455</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>31</v>
@@ -18862,7 +18872,7 @@
         <v>106</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="3" t="s">
@@ -18889,7 +18899,7 @@
     </row>
     <row r="43" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>400</v>
@@ -18904,7 +18914,7 @@
         <v>455</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>31</v>
@@ -18925,7 +18935,7 @@
         <v>106</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="Q43" s="3"/>
       <c r="R43" s="3" t="s">
@@ -18952,7 +18962,7 @@
     </row>
     <row r="44" spans="1:28" s="2" customFormat="1" ht="99" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>400</v>
@@ -18967,7 +18977,7 @@
         <v>455</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>31</v>
@@ -18988,7 +18998,7 @@
         <v>106</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="Q44" s="3"/>
       <c r="R44" s="3" t="s">
@@ -19015,7 +19025,7 @@
     </row>
     <row r="45" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>400</v>
@@ -19030,7 +19040,7 @@
         <v>459</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>31</v>
@@ -19051,7 +19061,7 @@
         <v>106</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3" t="s">
@@ -19078,7 +19088,7 @@
     </row>
     <row r="46" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>400</v>
@@ -19093,7 +19103,7 @@
         <v>459</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>31</v>
@@ -19114,7 +19124,7 @@
         <v>106</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
@@ -19141,7 +19151,7 @@
     </row>
     <row r="47" spans="1:28" s="2" customFormat="1" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>400</v>
@@ -19156,7 +19166,7 @@
         <v>459</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>31</v>
@@ -19177,7 +19187,7 @@
         <v>106</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="Q47" s="3"/>
       <c r="R47" s="3" t="s">
